--- a/template/school-template.xlsx
+++ b/template/school-template.xlsx
@@ -940,7 +940,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C18"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="70.83203125" customWidth="1"/>
@@ -1092,18 +1092,62 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
+        <v>Blood group</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Shown as a red badge on the card. Use a dropdown in your form so you do not collect "o positive" and "O +ve".</v>
+      </c>
+      <c r="C14" t="str">
+        <v>कार्ड पर लाल बैज में दिखता है। फ़ॉर्म में ड्रॉपडाउन रखें।</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Optional fields</v>
+      </c>
+      <c r="B15" t="str">
+        <v>The first two extra columns show on the card; the rest fold behind a More details button. Search still finds them and opens the card.</v>
+      </c>
+      <c r="C15" t="str">
+        <v>पहले दो अतिरिक्त कॉलम कार्ड पर दिखते हैं, बाक़ी "More details" के पीछे। खोज उन्हें भी ढूँढ लेती है।</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Owner columns</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Fill Owner Name / Owner Phone / Owner Address only for tenanted flats. They appear behind an Owner details button; leave blank and nothing is shown.</v>
+      </c>
+      <c r="C16" t="str">
+        <v>किरायेदार वाले फ्लैट के लिए ही भरें। खाली छोड़ने पर कुछ नहीं दिखेगा।</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>_Private sheet</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Dates of birth, medical notes, lease dates and police verification live here. The leading underscore keeps the sheet off the website entirely.</v>
+      </c>
+      <c r="C17" t="str">
+        <v>जन्मतिथि, चिकित्सा जानकारी आदि यहाँ रखें। यह शीट वेबसाइट पर कभी नहीं दिखती।</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
         <v>Examples</v>
       </c>
-      <c r="B14" t="str">
+      <c r="B18" t="str">
         <v>Delete the example rows before publishing.</v>
       </c>
-      <c r="C14" t="str">
+      <c r="C18" t="str">
         <v>प्रकाशित करने से पहले उदाहरण पंक्तियाँ हटा दें।</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C18"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/template/school-template.xlsx
+++ b/template/school-template.xlsx
@@ -4,12 +4,13 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="Staff" sheetId="2" r:id="rId2"/>
-    <sheet name="Emergency" sheetId="3" r:id="rId3"/>
-    <sheet name="Classes" sheetId="4" r:id="rId4"/>
-    <sheet name="Parents" sheetId="5" r:id="rId5"/>
-    <sheet name="Documents" sheetId="6" r:id="rId6"/>
-    <sheet name="_Read me" sheetId="7" r:id="rId7"/>
+    <sheet name="Notices" sheetId="2" r:id="rId2"/>
+    <sheet name="Staff" sheetId="3" r:id="rId3"/>
+    <sheet name="Emergency" sheetId="4" r:id="rId4"/>
+    <sheet name="Classes" sheetId="5" r:id="rId5"/>
+    <sheet name="Parents" sheetId="6" r:id="rId6"/>
+    <sheet name="Documents" sheetId="7" r:id="rId7"/>
+    <sheet name="_Read me" sheetId="8" r:id="rId8"/>
   </sheets>
 </workbook>
 </file>
@@ -403,7 +404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C17"/>
   <cols>
     <col min="1" max="1" width="26.83203125" customWidth="1"/>
     <col min="2" max="2" width="62.83203125" customWidth="1"/>
@@ -533,10 +534,10 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Hindi: Staff</v>
+        <v>Hindi: Notices</v>
       </c>
       <c r="B12" t="str">
-        <v>स्टाफ</v>
+        <v>सूचनाएँ</v>
       </c>
       <c r="C12" t="str">
         <v>हिंदी में अनुभाग का नाम</v>
@@ -544,10 +545,10 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Hindi: Emergency</v>
+        <v>Hindi: Staff</v>
       </c>
       <c r="B13" t="str">
-        <v>आपातकालीन संपर्क</v>
+        <v>स्टाफ</v>
       </c>
       <c r="C13" t="str">
         <v>हिंदी में अनुभाग का नाम</v>
@@ -555,10 +556,10 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Hindi: Classes</v>
+        <v>Hindi: Emergency</v>
       </c>
       <c r="B14" t="str">
-        <v>कक्षाएँ</v>
+        <v>आपातकालीन संपर्क</v>
       </c>
       <c r="C14" t="str">
         <v>हिंदी में अनुभाग का नाम</v>
@@ -566,10 +567,10 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Hindi: Parents</v>
+        <v>Hindi: Classes</v>
       </c>
       <c r="B15" t="str">
-        <v>अभिभावक</v>
+        <v>कक्षाएँ</v>
       </c>
       <c r="C15" t="str">
         <v>हिंदी में अनुभाग का नाम</v>
@@ -577,23 +578,113 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Hindi: Documents</v>
+        <v>Hindi: Parents</v>
       </c>
       <c r="B16" t="str">
-        <v>दस्तावेज़</v>
+        <v>अभिभावक</v>
       </c>
       <c r="C16" t="str">
         <v>हिंदी में अनुभाग का नाम</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Hindi: Documents</v>
+      </c>
+      <c r="B17" t="str">
+        <v>दस्तावेज़</v>
+      </c>
+      <c r="C17" t="str">
+        <v>हिंदी में अनुभाग का नाम</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C17"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F3"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="40.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="12.83203125" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Date</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Title</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Details</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Category</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Pinned</v>
+      </c>
+      <c r="F1" t="str">
+        <v>File</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>2026-04-01</v>
+      </c>
+      <c r="B2" t="str">
+        <v>First announcement — pinned to the top</v>
+      </c>
+      <c r="C2" t="str">
+        <v>The full text of the notice goes here.</v>
+      </c>
+      <c r="D2" t="str">
+        <v>General</v>
+      </c>
+      <c r="E2" t="str">
+        <v>yes</v>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>2026-03-28</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Second announcement</v>
+      </c>
+      <c r="C3" t="str">
+        <v/>
+      </c>
+      <c r="D3" t="str">
+        <v>General</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F3"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E3"/>
   <cols>
@@ -662,7 +753,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D3"/>
   <cols>
@@ -721,7 +812,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F3"/>
   <cols>
@@ -800,7 +891,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E3"/>
   <cols>
@@ -869,7 +960,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E3"/>
   <cols>
@@ -908,7 +999,7 @@
         <v>materials/example.pdf</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-08-24</v>
+        <v>2026-08-25</v>
       </c>
       <c r="E2" t="str">
         <v>Anything worth knowing</v>
@@ -925,7 +1016,7 @@
         <v>materials/example.pdf</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-08-24</v>
+        <v>2026-08-25</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -938,7 +1029,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C18"/>
   <cols>

--- a/template/school-template.xlsx
+++ b/template/school-template.xlsx
@@ -999,7 +999,7 @@
         <v>materials/example.pdf</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-08-25</v>
+        <v>2026-08-29</v>
       </c>
       <c r="E2" t="str">
         <v>Anything worth knowing</v>
@@ -1016,7 +1016,7 @@
         <v>materials/example.pdf</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-08-25</v>
+        <v>2026-08-29</v>
       </c>
       <c r="E3" t="str">
         <v/>
